--- a/temp/menu_template.xlsx
+++ b/temp/menu_template.xlsx
@@ -415,13 +415,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -442,6 +443,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Food Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
@@ -462,7 +468,12 @@
           <t>BR001</t>
         </is>
       </c>
-      <c r="D2" t="b">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>veg</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
         <v>1</v>
       </c>
     </row>
